--- a/evals_comparative_op_params/test01/analysis_output_baseline/perf_report_trace2.xlsx
+++ b/evals_comparative_op_params/test01/analysis_output_baseline/perf_report_trace2.xlsx
@@ -936,12 +936,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t&gt;&gt;', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(280.0), 'mean_duration_us': np.float64(280.0), 'median_duration_us': np.float64(280.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(280.0), 'max_duration_us': np.float64(280.0)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(280.0), 'mean_duration_us': np.float64(280.0), 'median_duration_us': np.float64(280.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(280.0), 'max_duration_us': np.float64(280.0)}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128,...', 'stream': 7, 'mean_duration_us': np.float64(280.0)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(280.0)}]</t>
         </is>
       </c>
       <c r="AA2" t="n">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t&gt;&gt;', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(280.0), 'mean_duration_us': np.float64(280.0), 'median_duration_us': np.float64(280.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(280.0), 'max_duration_us': np.float64(280.0)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(280.0), 'mean_duration_us': np.float64(280.0), 'median_duration_us': np.float64(280.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(280.0), 'max_duration_us': np.float64(280.0)}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128,...', 'stream': 7, 'mean_duration_us': np.float64(280.0)}]</t>
+          <t>[{'name': 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_ke...', 'stream': 7, 'mean_duration_us': np.float64(280.0)}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>['attention', 'aten::scaled_dot_product_attention', 'flash_fwd_hdim64_bf16_sm80&lt;Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t&gt;&gt;']</t>
+          <t>['attention', 'aten::scaled_dot_product_attention', 'void pytorch_flash::flash_fwd_kernel&lt;pytorch_flash::Flash_fwd_kernel_traits&lt;64, 128, 128, 4, false, false, cutlass::bfloat16_t, pytorch_flash::Flash_kernel_traits&lt;64, 128, 128, 4, cutlass::bfloat16_t&gt; &gt;, false, true, false, false, false, true, false&gt;(pytorch_flash::Flash_fwd_params)']</t>
         </is>
       </c>
       <c r="AD2" t="n">
